--- a/output/pdf_financials_xlsx/LPS.xlsx
+++ b/output/pdf_financials_xlsx/LPS.xlsx
@@ -5957,19 +5957,19 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>1.994656</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>4.325512</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>5.091396</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>5.716802</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>7.383995</v>
       </c>
       <c r="G92" s="3" t="n">
         <v>7.640496</v>
@@ -6577,31 +6577,31 @@
         <v>-0.098222</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>0</v>
+        <v>-0.02676</v>
       </c>
       <c r="H103" s="3" t="n">
-        <v>0</v>
+        <v>-0.308491</v>
       </c>
       <c r="I103" s="3" t="n">
-        <v>0</v>
+        <v>-1.2836</v>
       </c>
       <c r="J103" s="3" t="n">
-        <v>0</v>
+        <v>0.014301</v>
       </c>
       <c r="K103" s="3" t="n">
-        <v>0</v>
+        <v>0.752607</v>
       </c>
       <c r="L103" s="3" t="n">
-        <v>0</v>
+        <v>-0.129282</v>
       </c>
       <c r="M103" s="3" t="n">
-        <v>0</v>
+        <v>0.316103</v>
       </c>
       <c r="N103" s="3" t="n">
-        <v>0</v>
+        <v>-0.343587</v>
       </c>
       <c r="O103" s="3" t="n">
-        <v>0</v>
+        <v>0.745221</v>
       </c>
       <c r="P103" s="1" t="inlineStr">
         <is>
@@ -6760,10 +6760,10 @@
         <v>-0.098222</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>-3.257054</v>
+        <v>-3.283814</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>-1.342128</v>
+        <v>-1.650619</v>
       </c>
       <c r="I106" s="3" t="n">
         <v>-3.863191</v>
@@ -18776,7 +18776,11 @@
           <t>Share-based payment reserve (Note 13)</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr"/>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E108" t="inlineStr">
         <is>
           <t>-</t>
@@ -19612,7 +19616,11 @@
           <t>Share-based payment reserve (Note 14)</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr"/>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E117" t="inlineStr">
         <is>
           <t>-</t>
@@ -20664,7 +20672,11 @@
           <t>Share‐based payment reserve (Note 13)</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr"/>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E128" s="5" t="n">
         <v>1.994656</v>
       </c>
@@ -21592,7 +21604,11 @@
           <t>Receivables, prepaids and deposits</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr"/>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E138" t="inlineStr">
         <is>
           <t>-</t>
@@ -24878,7 +24894,11 @@
           <t>Receivables, prepaids and deposits</t>
         </is>
       </c>
-      <c r="D173" t="inlineStr"/>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E173" t="inlineStr">
         <is>
           <t>-</t>
@@ -29062,7 +29082,11 @@
           <t>(Increase) in receivables, prepaids and deposits 14</t>
         </is>
       </c>
-      <c r="D217" t="inlineStr"/>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E217" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/LPS.xlsx
+++ b/output/pdf_financials_xlsx/LPS.xlsx
@@ -999,16 +999,16 @@
         </is>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0</v>
+        <v>5.291444</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0</v>
+        <v>4.6128</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0</v>
+        <v>5.570858</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>0</v>
+        <v>4.430493</v>
       </c>
       <c r="P10" s="1" t="inlineStr">
         <is>
@@ -2567,22 +2567,22 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.017367</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.604203</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.02152</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.001698</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>2.410077</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.536116</v>
       </c>
       <c r="H34" s="1" t="inlineStr">
         <is>
@@ -2681,22 +2681,22 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.017367</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.604203</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.02152</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.001698</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>2.410077</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.536116</v>
       </c>
       <c r="H36" s="1" t="inlineStr">
         <is>
@@ -3365,22 +3365,22 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.161431</v>
+        <v>0.144064</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.678</v>
+        <v>0.073797</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.07552</v>
+        <v>0.054</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.08358</v>
+        <v>0.081882</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>2.5032</v>
+        <v>0.093123</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.6187049999999999</v>
+        <v>0.082589</v>
       </c>
       <c r="H48" s="1" t="inlineStr">
         <is>
@@ -16074,7 +16074,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -17650,7 +17650,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E96" s="5" t="n">
@@ -34186,7 +34186,7 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
@@ -35614,7 +35614,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">

--- a/output/pdf_financials_xlsx/LPS.xlsx
+++ b/output/pdf_financials_xlsx/LPS.xlsx
@@ -2230,16 +2230,16 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0</v>
+        <v>0.079682</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0</v>
+        <v>0.026857</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0</v>
+        <v>0.014277</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0</v>
+        <v>0.009102000000000001</v>
       </c>
       <c r="G28" s="3" t="n">
         <v>0.180562</v>
@@ -2297,16 +2297,16 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-2.486005</v>
+        <v>-2.406323</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-2.215207</v>
+        <v>-2.18835</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-2.146544</v>
+        <v>-2.132267</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-2.011323</v>
+        <v>-2.002221</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>-2.695955</v>
@@ -2364,16 +2364,16 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-936.5988644797667</v>
+        <v>-906.57878378022</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-1884.240207544762</v>
+        <v>-1861.395823586952</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-589.4491722067986</v>
+        <v>-585.5286535351122</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-239.0720833372954</v>
+        <v>-237.9901914171334</v>
       </c>
       <c r="G30" s="3" t="n">
         <v>-1328.423111794387</v>
@@ -6382,16 +6382,16 @@
         </is>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>0.079682</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>0.026857</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>0.014277</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>0.009102000000000001</v>
       </c>
       <c r="G100" s="3" t="n">
         <v>0.180562</v>
@@ -7144,7 +7144,7 @@
         <v>0</v>
       </c>
       <c r="M112" s="3" t="n">
-        <v>0</v>
+        <v>0.001597</v>
       </c>
       <c r="N112" s="3" t="n">
         <v>0</v>
@@ -23944,7 +23944,11 @@
           <t>Proceeds from disposal of property and equipment 7</t>
         </is>
       </c>
-      <c r="D163" t="inlineStr"/>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E163" t="inlineStr">
         <is>
           <t>-</t>
@@ -30234,7 +30238,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D229" t="inlineStr"/>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E229" t="inlineStr">
         <is>
           <t>-</t>
@@ -39224,7 +39232,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D324" t="inlineStr"/>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E324" t="inlineStr">
         <is>
           <t>-</t>
